--- a/Database.xlsx
+++ b/Database.xlsx
@@ -684,7 +684,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2231 W Cicago Ave</t>
+          <t>2231 W Chicago Ave</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -717,8 +717,12 @@
           <t>https://radc.hoover.org/?a=d&amp;d=RADCaakh19180706-01.1.4&amp;e=-------en-10--1--img-------</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>41.8957034184145</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-87.6831680796444</v>
+      </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2163,8 +2167,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>41.9115468252795</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-87.70243787473539</v>
+      </c>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2229,8 +2237,12 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>41.7414612545311</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-87.542630027576</v>
+      </c>
       <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2260,8 +2272,12 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>41.8979909034197</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-87.67112740917619</v>
+      </c>
       <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2470,8 +2486,12 @@
           <t>https://www.loc.gov/resource/sn82015743/1926-12-01/ed-1/?sp=3&amp;st=image&amp;r=0.371,1.159,0.488,0.174,1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>41.8831146613135</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-87.6340120490165</v>
+      </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -3679,10 +3699,10 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>27.721699</v>
+        <v>41.8636480569162</v>
       </c>
       <c r="L27" t="n">
-        <v>-81.5461308</v>
+        <v>-87.8681870233677</v>
       </c>
       <c r="M27" t="inlineStr"/>
     </row>
@@ -3944,7 +3964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4352,10 +4372,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27.721699</v>
+        <v>41.8636480569162</v>
       </c>
       <c r="L8" t="n">
-        <v>-81.5461308</v>
+        <v>-87.8681870233677</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -6257,8 +6277,12 @@
           <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="n">
+        <v>41.8818841713731</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-87.6310140678812</v>
+      </c>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6978,8 +7002,12 @@
         <v>1</v>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>41.8233922939177</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-87.70887127835741</v>
+      </c>
       <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -8014,26 +8042,26 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>138 Passaic St</t>
+          <t>3131 West 42th st</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>потребительские товары</t>
+          <t>продажа вещей</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>A. Stetz Feather Co.</t>
+          <t>Пивень</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>готовые подушки и перины</t>
+          <t>5-ти комнатная мебель оптово или поштучно</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8051,36 +8079,30 @@
         <v>1</v>
       </c>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="n">
-        <v>40.7549518</v>
-      </c>
-      <c r="L84" t="n">
-        <v>-74.16626359999999</v>
-      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>115</v>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3131 West 42th st</t>
+          <t>1027 Milwaukee ave</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>продажа вещей</t>
+          <t>потребительские товары</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Пивень</t>
+          <t>Bednarz</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5-ти комнатная мебель оптово или поштучно</t>
+          <t>продаются хроматические гармони, ручная работа, цены умеренные</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8098,30 +8120,34 @@
         <v>1</v>
       </c>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>41.9006835</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-87.6617732</v>
+      </c>
       <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1027 Milwaukee ave</t>
+          <t>1808 S Ashland Ave</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>потребительские товары</t>
+          <t>продажа жилья</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bednarz</t>
+          <t>Strnad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>продаются хроматические гармони, ручная работа, цены умеренные</t>
+          <t>Новый кирпичный бунгало за 2000 долларов</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8140,10 +8166,10 @@
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
-        <v>41.9006835</v>
+        <v>41.8574615</v>
       </c>
       <c r="L86" t="n">
-        <v>-87.6617732</v>
+        <v>-87.6664681</v>
       </c>
       <c r="M86" t="inlineStr"/>
     </row>
@@ -8151,22 +8177,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1808 S Ashland Ave</t>
+          <t>1923 W Division St</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>продажа жилья</t>
+          <t>коммерческая недвижимость</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Strnad</t>
+          <t>частное объявление</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Новый кирпичный бунгало за 2000 долларов</t>
+          <t>мясная лавка в бойком районе за 1/4 цены</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8185,10 +8211,10 @@
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="n">
-        <v>41.8574615</v>
+        <v>41.9029932</v>
       </c>
       <c r="L87" t="n">
-        <v>-87.6664681</v>
+        <v>-87.67576219999999</v>
       </c>
       <c r="M87" t="inlineStr"/>
     </row>
@@ -8196,22 +8222,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1923 W Division St</t>
+          <t>127 N Dearborn St</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>коммерческая недвижимость</t>
+          <t>адвокат</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>частное объявление</t>
+          <t>Zavertnik</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>мясная лавка в бойком районе за 1/4 цены</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8230,10 +8256,10 @@
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
-        <v>41.9029932</v>
+        <v>41.8847559</v>
       </c>
       <c r="L88" t="n">
-        <v>-87.67576219999999</v>
+        <v>-87.62957729999999</v>
       </c>
       <c r="M88" t="inlineStr"/>
     </row>
@@ -8241,22 +8267,22 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>127 N Dearborn St</t>
+          <t>809 W 35th St</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>адвокат</t>
+          <t>нотариус</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Zavertnik</t>
+          <t>S. L. Fabian and Co</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Моргичес, нотариус, перевод денег</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8275,10 +8301,10 @@
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
-        <v>41.8847559</v>
+        <v>41.8306639</v>
       </c>
       <c r="L89" t="n">
-        <v>-87.62957729999999</v>
+        <v>-87.646435</v>
       </c>
       <c r="M89" t="inlineStr"/>
     </row>
@@ -8286,22 +8312,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>809 W 35th St</t>
+          <t>813 N Paulina St</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>нотариус</t>
+          <t>адвокат</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>S. L. Fabian and Co</t>
+          <t>Валтон</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Моргичес, нотариус, перевод денег</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8320,10 +8346,10 @@
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
-        <v>41.8306639</v>
+        <v>41.8965015433095</v>
       </c>
       <c r="L90" t="n">
-        <v>-87.646435</v>
+        <v>-87.6697739625109</v>
       </c>
       <c r="M90" t="inlineStr"/>
     </row>
@@ -8331,22 +8357,22 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>813 N Paulina St</t>
+          <t>3451 N Avers Ave</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>адвокат</t>
+          <t>рабочий</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Валтон</t>
+          <t>Frank Ryniecki and Co.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>контракторы</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8365,10 +8391,10 @@
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
-        <v>41.8965015433095</v>
+        <v>41.9443208</v>
       </c>
       <c r="L91" t="n">
-        <v>-87.6697739625109</v>
+        <v>-87.72337810000001</v>
       </c>
       <c r="M91" t="inlineStr"/>
     </row>
@@ -8376,7 +8402,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3451 N Avers Ave</t>
+          <t>5539 W Belmont</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8386,12 +8412,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Frank Ryniecki and Co.</t>
+          <t>INDependence Construction Co</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>контракторы</t>
+          <t>Русская строительная контора</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8410,10 +8436,10 @@
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
-        <v>41.9443208</v>
+        <v>41.9385053</v>
       </c>
       <c r="L92" t="n">
-        <v>-87.72337810000001</v>
+        <v>-87.7654883</v>
       </c>
       <c r="M92" t="inlineStr"/>
     </row>
@@ -8421,22 +8447,22 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5539 W Belmont</t>
+          <t>3152 W Roosevelt Rd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>рабочий</t>
+          <t>врач</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>INDependence Construction Co</t>
+          <t>Др Гиман В Бау</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Русская строительная контора</t>
+          <t>Ухо, нос и горло</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8448,17 +8474,17 @@
         <v>1927</v>
       </c>
       <c r="H93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="n">
-        <v>41.9385053</v>
+        <v>41.8664976</v>
       </c>
       <c r="L93" t="n">
-        <v>-87.7654883</v>
+        <v>-87.7050874</v>
       </c>
       <c r="M93" t="inlineStr"/>
     </row>
@@ -8476,12 +8502,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Др Гиман В Бау</t>
+          <t>Др Дж Зун</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ухо, нос и горло</t>
+          <t>Зубной</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8511,7 +8537,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3152 W Roosevelt Rd</t>
+          <t>4204 Archer Ave</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8521,7 +8547,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Др Дж Зун</t>
+          <t>Др П. Л. Чадович</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8545,10 +8571,10 @@
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
-        <v>41.8664976</v>
+        <v>41.8169895</v>
       </c>
       <c r="L95" t="n">
-        <v>-87.7050874</v>
+        <v>-87.6996915</v>
       </c>
       <c r="M95" t="inlineStr"/>
     </row>
@@ -8556,7 +8582,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4204 Archer Ave</t>
+          <t>1756 W Division St</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8590,10 +8616,10 @@
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>41.8169895</v>
+        <v>41.9033594</v>
       </c>
       <c r="L96" t="n">
-        <v>-87.6996915</v>
+        <v>-87.67168820000001</v>
       </c>
       <c r="M96" t="inlineStr"/>
     </row>
@@ -8601,22 +8627,22 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1756 W Division St</t>
+          <t>1402 N Paulina St</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>врач</t>
+          <t>коммерческая недвижимость</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Др П. Л. Чадович</t>
+          <t>частное объявление</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Зубной</t>
+          <t>продается бутчерня и гроссерня в польско-литовской колонии</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8635,10 +8661,10 @@
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
-        <v>41.9033594</v>
+        <v>41.906892</v>
       </c>
       <c r="L97" t="n">
-        <v>-87.67168820000001</v>
+        <v>-87.670137</v>
       </c>
       <c r="M97" t="inlineStr"/>
     </row>
@@ -8646,12 +8672,12 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1402 N Paulina St</t>
+          <t>1017 N Wood</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>коммерческая недвижимость</t>
+          <t>продажа вещей</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8661,7 +8687,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>продается бутчерня и гроссерня в польско-литовской колонии</t>
+          <t>Дешево продается мебель и новая белая печка</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8680,10 +8706,10 @@
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="n">
-        <v>41.906892</v>
+        <v>41.900223</v>
       </c>
       <c r="L98" t="n">
-        <v>-87.670137</v>
+        <v>-87.6720337</v>
       </c>
       <c r="M98" t="inlineStr"/>
     </row>
@@ -8691,22 +8717,22 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1017 N Wood</t>
+          <t>2057 W 22 st</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>продажа вещей</t>
+          <t>продажа жилья</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>частное объявление</t>
+          <t>A S Plecho and Co</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Дешево продается мебель и новая белая печка</t>
+          <t>Продаем фармы, дома, торговые предприятия</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8725,10 +8751,10 @@
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
-        <v>41.900223</v>
+        <v>42.1902504</v>
       </c>
       <c r="L99" t="n">
-        <v>-87.6720337</v>
+        <v>-88.10135940000001</v>
       </c>
       <c r="M99" t="inlineStr"/>
     </row>
@@ -8736,22 +8762,22 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2057 W 22 st</t>
+          <t>624 S Michigan Ave</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>продажа жилья</t>
+          <t>вакансия</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A S Plecho and Co</t>
+          <t>господин Лесик</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Продаем фармы, дома, торговые предприятия</t>
+          <t>требуются для легкой и выгодной работы мужчины и женщины со знанием русского языка</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8770,10 +8796,10 @@
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
-        <v>42.1902504</v>
+        <v>41.8735823</v>
       </c>
       <c r="L100" t="n">
-        <v>-88.10135940000001</v>
+        <v>-87.6245054</v>
       </c>
       <c r="M100" t="inlineStr"/>
     </row>
@@ -8781,22 +8807,22 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>624 S Michigan Ave</t>
+          <t>403 S Wabash Ave</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>вакансия</t>
+          <t>ресторан</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>господин Лесик</t>
+          <t>ресторан Петрушка</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>требуются для легкой и выгодной работы мужчины и женщины со знанием русского языка</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8815,10 +8841,10 @@
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>41.8735823</v>
+        <v>41.8768707</v>
       </c>
       <c r="L101" t="n">
-        <v>-87.6245054</v>
+        <v>-87.6261645</v>
       </c>
       <c r="M101" t="inlineStr"/>
     </row>
@@ -8831,7 +8857,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ресторан</t>
+          <t>вакансия</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8841,7 +8867,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>требуется швейцар</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8871,22 +8897,22 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>403 S Wabash Ave</t>
+          <t>1346 W 14th st</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>вакансия</t>
+          <t>ремесленник</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ресторан Петрушка</t>
+          <t>Даниил Кот</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>требуется швейцар</t>
+          <t>русский портной</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8905,10 +8931,10 @@
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>41.8768707</v>
+        <v>41.8634429</v>
       </c>
       <c r="L103" t="n">
-        <v>-87.6261645</v>
+        <v>-87.6601778</v>
       </c>
       <c r="M103" t="inlineStr"/>
     </row>
@@ -8916,7 +8942,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1346 W 14th st</t>
+          <t>742 E 105 Pl</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8926,12 +8952,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Даниил Кот</t>
+          <t>Mshar</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>русский портной</t>
+          <t>русский плотник</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8950,10 +8976,10 @@
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>41.8634429</v>
+        <v>41.7030387101996</v>
       </c>
       <c r="L104" t="n">
-        <v>-87.6601778</v>
+        <v>-87.6046693625252</v>
       </c>
       <c r="M104" t="inlineStr"/>
     </row>
@@ -8961,22 +8987,22 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>742 E 105 Pl</t>
+          <t>1200 N Ashland Ave</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ремесленник</t>
+          <t>врач</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mshar</t>
+          <t>Кселовский</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>русский плотник</t>
+          <t>Хирург</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8988,17 +9014,17 @@
         <v>1927</v>
       </c>
       <c r="H105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
-        <v>41.7030387101996</v>
+        <v>41.9037547</v>
       </c>
       <c r="L105" t="n">
-        <v>-87.6046693625252</v>
+        <v>-87.66752320000001</v>
       </c>
       <c r="M105" t="inlineStr"/>
     </row>
@@ -9006,22 +9032,22 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1200 N Ashland Ave</t>
+          <t>1553 W Chicago Ave</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>врач</t>
+          <t>потребительские товары</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Кселовский</t>
+          <t>П. Кворка и сыновья</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Хирург</t>
+          <t>Мебель, печи, пианино, костюмы за наличные и в рассрочку</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -9040,10 +9066,10 @@
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>41.9037547</v>
+        <v>41.8958009</v>
       </c>
       <c r="L106" t="n">
-        <v>-87.66752320000001</v>
+        <v>-87.66692449999999</v>
       </c>
       <c r="M106" t="inlineStr"/>
     </row>
@@ -9051,22 +9077,22 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1553 W Chicago Ave</t>
+          <t>614 State St</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>потребительские товары</t>
+          <t>продажа жилья</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>П. Кворка и сыновья</t>
+          <t>частное объявление</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Мебель, печи, пианино, костюмы за наличные и в рассрочку</t>
+          <t>продается весьма доходное имущество, 5 квартир, водяное отопление, 3 местный гараж</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -9085,33 +9111,37 @@
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>41.8958009</v>
+        <v>41.8747807560033</v>
       </c>
       <c r="L107" t="n">
-        <v>-87.66692449999999</v>
-      </c>
-      <c r="M107" t="inlineStr"/>
+        <v>-87.6277195759839</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Unsure - might be either N or S State</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>614 State St</t>
+          <t>310 S Michigan Ave</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>продажа жилья</t>
+          <t>вакансия</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>частное объявление</t>
+          <t>Pierce Richard and Co</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>продается весьма доходное имущество, 5 квартир, водяное отопление, 3 местный гараж</t>
+          <t>Требуется стенографистка</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9130,61 +9160,12 @@
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>40.1816726</v>
+        <v>41.8779893</v>
       </c>
       <c r="L108" t="n">
-        <v>-91.377397</v>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>Unsure</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>310 S Michigan Ave</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>вакансия</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Pierce Richard and Co</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Требуется стенографистка</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Rassvet =: The dawn</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>1927</v>
-      </c>
-      <c r="H109" t="n">
-        <v>12</v>
-      </c>
-      <c r="I109" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="n">
-        <v>41.8779893</v>
-      </c>
-      <c r="L109" t="n">
         <v>-87.6246979</v>
       </c>
-      <c r="M109" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10137,8 +10118,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19280102-01&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>41.8641168347131</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-87.6469914738307</v>
+      </c>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -10721,8 +10706,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19280102-01&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>41.7027169818782</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-87.60464001430149</v>
+      </c>
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -11284,8 +11273,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19380103-01.1.3&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>41.9039636653434</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-87.6809636910552</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -11329,8 +11322,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19380103-01.1.3&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>41.8622479615596</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-87.6947971187479</v>
+      </c>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -11375,7 +11372,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>41.8162529</v>
+        <v>41.8162038972745</v>
       </c>
       <c r="L11" t="n">
         <v>-87.7011837</v>
@@ -12061,12 +12058,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>42.8010375</v>
+        <v>41.827236724536</v>
       </c>
       <c r="L25" t="n">
-        <v>-85.513918</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+        <v>-87.7361017026942</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>The original building is prob demolished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -12158,8 +12159,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19380303-01.1.4&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>41.9682791324609</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-87.73480905163539</v>
+      </c>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -12252,8 +12257,12 @@
           <t>https://idnc.library.illinois.edu/?a=d&amp;d=RAS19380502-01.1.4&amp;e=-------en-20--1--txt-txIN----------</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>41.9237172347172</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-87.77492783116161</v>
+      </c>
       <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
